--- a/Book2.xlsx
+++ b/Book2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Stage_Lucas_Chabert\Donné\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FB06E5-6EEE-4C3F-925F-38E29B84F322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3304B2F2-4933-48C9-9E22-BF6DFFC1FC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D07937D3-E158-41EE-A4D8-6B40014C1ACE}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D07937D3-E158-41EE-A4D8-6B40014C1ACE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
     <t>tour</t>
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>C (2)</t>
   </si>
 </sst>
 </file>
@@ -147,14 +150,27 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:ln w="38100" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -294,10 +310,121 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-48AA-45E2-B66E-BB32607B37FA}"/>
+              <c16:uniqueId val="{00000000-D624-4C3A-8118-53F380DDD3F6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D624-4C3A-8118-53F380DDD3F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -309,11 +436,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="86810080"/>
-        <c:axId val="86806720"/>
+        <c:axId val="1383927696"/>
+        <c:axId val="1383918096"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="86810080"/>
+        <c:axId val="1383927696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -370,12 +497,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86806720"/>
+        <c:crossAx val="1383918096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="86806720"/>
+        <c:axId val="1383918096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -432,7 +559,427 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86810080"/>
+        <c:crossAx val="1383927696"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>1.26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.29</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.31</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3320000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.47</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.53</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.63</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.73</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.68</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.59</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.47</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.36</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.31</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C13E-4D83-8BD0-E3B641BDE038}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1383925776"/>
+        <c:axId val="1383926736"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1383925776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1383926736"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1383926736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1383925776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -528,6 +1075,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1044,27 +1631,543 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>80010</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>80010</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3A63A8D-9A80-4CB0-4378-6D9D0BAA11EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96789DC1-5671-0AE6-4DBD-37AC196526E9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1077,6 +2180,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DDF6C14-8C02-A5EE-8FA2-F7D04C00F27D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1402,26 +2541,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A82ACEC-8FB0-4978-9A48-0FB6A4FBEE3D}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
         <v>1.3</v>
       </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1.26</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>A2+1/8</f>
         <v>0.125</v>
@@ -1429,17 +2580,31 @@
       <c r="B3">
         <v>1.4</v>
       </c>
+      <c r="D3">
+        <f>1/8</f>
+        <v>0.125</v>
+      </c>
+      <c r="E3">
+        <v>1.29</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
-        <f t="shared" ref="A4:A21" si="0">A3+1/8</f>
+        <f t="shared" ref="A4:A10" si="0">A3+1/8</f>
         <v>0.25</v>
       </c>
       <c r="B4">
         <v>1.53</v>
       </c>
+      <c r="D4">
+        <f>1/8+D3</f>
+        <v>0.25</v>
+      </c>
+      <c r="E4">
+        <v>1.31</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>0.375</v>
@@ -1447,8 +2612,15 @@
       <c r="B5">
         <v>1.72</v>
       </c>
+      <c r="D5">
+        <f t="shared" ref="D5:D18" si="1">1/8+D4</f>
+        <v>0.375</v>
+      </c>
+      <c r="E5">
+        <v>1.3320000000000001</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -1456,8 +2628,15 @@
       <c r="B6">
         <v>1.73</v>
       </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>1.3859999999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>0.625</v>
@@ -1465,8 +2644,15 @@
       <c r="B7">
         <v>1.9</v>
       </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>0.625</v>
+      </c>
+      <c r="E7">
+        <v>1.47</v>
+      </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>0.75</v>
@@ -1474,8 +2660,15 @@
       <c r="B8">
         <v>2</v>
       </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E8">
+        <v>1.53</v>
+      </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>0.875</v>
@@ -1483,8 +2676,15 @@
       <c r="B9">
         <v>2.2000000000000002</v>
       </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E9">
+        <v>1.63</v>
+      </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1492,8 +2692,15 @@
       <c r="B10">
         <v>2.5</v>
       </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1.73</v>
+      </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>A10-1/8</f>
         <v>0.875</v>
@@ -1501,68 +2708,124 @@
       <c r="B11">
         <v>2.4</v>
       </c>
+      <c r="D11">
+        <f>-1/8+D10</f>
+        <v>0.875</v>
+      </c>
+      <c r="E11">
+        <v>1.7</v>
+      </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
-        <f t="shared" ref="A12:A21" si="1">A11-1/8</f>
+        <f t="shared" ref="A12:A18" si="2">A11-1/8</f>
         <v>0.75</v>
       </c>
       <c r="B12">
         <v>2.4</v>
       </c>
+      <c r="D12">
+        <f t="shared" ref="D12:D34" si="3">-1/8+D11</f>
+        <v>0.75</v>
+      </c>
+      <c r="E12">
+        <v>1.68</v>
+      </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.625</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
+      <c r="D13">
+        <f t="shared" si="3"/>
+        <v>0.625</v>
+      </c>
+      <c r="E13">
+        <v>1.59</v>
+      </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="B14">
         <v>1.89</v>
       </c>
+      <c r="D14">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="E14">
+        <v>1.47</v>
+      </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.375</v>
       </c>
       <c r="B15">
         <v>1.7</v>
       </c>
+      <c r="D15">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="E15">
+        <v>1.36</v>
+      </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
       <c r="B16">
         <v>1.45</v>
       </c>
+      <c r="D16">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E16">
+        <v>1.35</v>
+      </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="B17">
         <v>1.07</v>
       </c>
+      <c r="D17">
+        <f t="shared" si="3"/>
+        <v>0.125</v>
+      </c>
+      <c r="E17">
+        <v>1.31</v>
+      </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="B18">
         <v>0.82</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Book2.xlsx
+++ b/Book2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Stage_Lucas_Chabert\Donné\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3304B2F2-4933-48C9-9E22-BF6DFFC1FC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0543DE-6F75-45BC-96BB-FC573AF86A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D07937D3-E158-41EE-A4D8-6B40014C1ACE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>tour</t>
   </si>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t>C (2)</t>
+  </si>
+  <si>
+    <t>c1(3)</t>
+  </si>
+  <si>
+    <t>c2(3)</t>
   </si>
 </sst>
 </file>
@@ -157,11 +163,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>Sheet1!$I$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>C</c:v>
+                  <c:v>c2(3)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -192,10 +198,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$18</c:f>
+              <c:f>Sheet1!$G$2:$G$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -224,27 +230,51 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>1.125</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.375</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.375</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.125</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>0.875</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="18">
                   <c:v>0.75</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="19">
                   <c:v>0.625</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="20">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="21">
                   <c:v>0.375</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="22">
                   <c:v>0.25</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="23">
                   <c:v>0.125</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="24">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -252,60 +282,84 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$18</c:f>
+              <c:f>Sheet1!$I$2:$I$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>1.3</c:v>
+                  <c:v>2.15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4</c:v>
+                  <c:v>2.1549999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.53</c:v>
+                  <c:v>2.16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.72</c:v>
+                  <c:v>2.19</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.73</c:v>
+                  <c:v>2.21</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
+                  <c:v>2.2679999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.2000000000000002</c:v>
+                  <c:v>2.2799999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.5</c:v>
+                  <c:v>2.34</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>2.37</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4420000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.448</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.4670000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.48</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.4700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.46</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>2.4</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.89</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.7</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.45</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1.07</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.82</c:v>
+                <c:pt idx="17">
+                  <c:v>2.37</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.2799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.2400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.21</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.16</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -313,118 +367,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D624-4C3A-8118-53F380DDD3F6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$18</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.125</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.375</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.625</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.625</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.375</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.125</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$2:$C$18</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D624-4C3A-8118-53F380DDD3F6}"/>
+              <c16:uniqueId val="{00000000-0367-458C-9D8F-D46831AEF89F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -436,11 +379,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1383927696"/>
-        <c:axId val="1383918096"/>
+        <c:axId val="1616531295"/>
+        <c:axId val="1616543775"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1383927696"/>
+        <c:axId val="1616531295"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -497,12 +440,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1383918096"/>
+        <c:crossAx val="1616543775"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1383918096"/>
+        <c:axId val="1616543775"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -559,427 +502,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1383927696"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="38100" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$2:$D$18</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.125</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.375</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.625</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.625</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.375</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.125</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$2:$E$18</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
-                <c:pt idx="0">
-                  <c:v>1.26</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.29</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.31</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.3320000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.3859999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.47</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.53</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.63</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.73</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.7</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.68</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.59</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.47</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.36</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.35</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1.31</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.27</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C13E-4D83-8BD0-E3B641BDE038}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1383925776"/>
-        <c:axId val="1383926736"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1383925776"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1383926736"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1383926736"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1383925776"/>
+        <c:crossAx val="1616531295"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1075,46 +598,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1631,543 +1114,27 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:rowOff>42862</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96789DC1-5671-0AE6-4DBD-37AC196526E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{885A7409-1672-CA5A-3774-7A0942320E54}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2180,42 +1147,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DDF6C14-8C02-A5EE-8FA2-F7D04C00F27D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2541,10 +1472,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A82ACEC-8FB0-4978-9A48-0FB6A4FBEE3D}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2557,8 +1488,17 @@
       <c r="E1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2571,8 +1511,17 @@
       <c r="E2">
         <v>1.26</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>4.8</v>
+      </c>
+      <c r="I2">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>A2+1/8</f>
         <v>0.125</v>
@@ -2587,8 +1536,18 @@
       <c r="E3">
         <v>1.29</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <f>1/8+G2</f>
+        <v>0.125</v>
+      </c>
+      <c r="H3">
+        <v>4.97</v>
+      </c>
+      <c r="I3">
+        <v>2.1549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ref="A4:A10" si="0">A3+1/8</f>
         <v>0.25</v>
@@ -2603,8 +1562,18 @@
       <c r="E4">
         <v>1.31</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <f t="shared" ref="G4:G18" si="1">1/8+G3</f>
+        <v>0.25</v>
+      </c>
+      <c r="H4">
+        <v>5.13</v>
+      </c>
+      <c r="I4">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>0.375</v>
@@ -2613,14 +1582,24 @@
         <v>1.72</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D18" si="1">1/8+D4</f>
+        <f t="shared" ref="D5:D10" si="2">1/8+D4</f>
         <v>0.375</v>
       </c>
       <c r="E5">
         <v>1.3320000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="H5">
+        <v>5.32</v>
+      </c>
+      <c r="I5">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -2629,14 +1608,24 @@
         <v>1.73</v>
       </c>
       <c r="D6">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>1.3859999999999999</v>
+      </c>
+      <c r="G6">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="E6">
-        <v>1.3859999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>5.55</v>
+      </c>
+      <c r="I6">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>0.625</v>
@@ -2645,14 +1634,24 @@
         <v>1.9</v>
       </c>
       <c r="D7">
+        <f t="shared" si="2"/>
+        <v>0.625</v>
+      </c>
+      <c r="E7">
+        <v>1.47</v>
+      </c>
+      <c r="G7">
         <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
-      <c r="E7">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>5.82</v>
+      </c>
+      <c r="I7">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>0.75</v>
@@ -2661,14 +1660,24 @@
         <v>2</v>
       </c>
       <c r="D8">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="E8">
+        <v>1.53</v>
+      </c>
+      <c r="G8">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="E8">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>6.11</v>
+      </c>
+      <c r="I8">
+        <v>2.2679999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>0.875</v>
@@ -2677,14 +1686,24 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D9">
+        <f t="shared" si="2"/>
+        <v>0.875</v>
+      </c>
+      <c r="E9">
+        <v>1.63</v>
+      </c>
+      <c r="G9">
         <f t="shared" si="1"/>
         <v>0.875</v>
       </c>
-      <c r="E9">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>6.44</v>
+      </c>
+      <c r="I9">
+        <v>2.2799999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2693,14 +1712,24 @@
         <v>2.5</v>
       </c>
       <c r="D10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1.73</v>
+      </c>
+      <c r="G10">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E10">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>6.87</v>
+      </c>
+      <c r="I10">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>A10-1/8</f>
         <v>0.875</v>
@@ -2715,117 +1744,293 @@
       <c r="E11">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>1.125</v>
+      </c>
+      <c r="H11">
+        <v>9.06</v>
+      </c>
+      <c r="I11">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
-        <f t="shared" ref="A12:A18" si="2">A11-1/8</f>
+        <f t="shared" ref="A12:A18" si="3">A11-1/8</f>
         <v>0.75</v>
       </c>
       <c r="B12">
         <v>2.4</v>
       </c>
       <c r="D12">
-        <f t="shared" ref="D12:D34" si="3">-1/8+D11</f>
+        <f t="shared" ref="D12:D18" si="4">-1/8+D11</f>
         <v>0.75</v>
       </c>
       <c r="E12">
         <v>1.68</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+      <c r="H12">
+        <v>11.29</v>
+      </c>
+      <c r="I12">
+        <v>2.4420000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.625</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="D13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.625</v>
       </c>
       <c r="E13">
         <v>1.59</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>1.375</v>
+      </c>
+      <c r="H13">
+        <v>13.3</v>
+      </c>
+      <c r="I13">
+        <v>2.448</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
       <c r="B14">
         <v>1.89</v>
       </c>
       <c r="D14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="E14">
         <v>1.47</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="H14">
+        <v>15.7</v>
+      </c>
+      <c r="I14">
+        <v>2.4670000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.375</v>
       </c>
       <c r="B15">
         <v>1.7</v>
       </c>
       <c r="D15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.375</v>
       </c>
       <c r="E15">
         <v>1.36</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <f>G14-1/8</f>
+        <v>1.375</v>
+      </c>
+      <c r="H15">
+        <v>14.39</v>
+      </c>
+      <c r="I15">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
       <c r="B16">
         <v>1.45</v>
       </c>
       <c r="D16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
       <c r="E16">
         <v>1.35</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <f t="shared" ref="G16:G26" si="5">G15-1/8</f>
+        <v>1.25</v>
+      </c>
+      <c r="H16">
+        <v>13.6</v>
+      </c>
+      <c r="I16">
+        <v>2.4700000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="B17">
         <v>1.07</v>
       </c>
       <c r="D17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E17">
         <v>1.31</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <f t="shared" si="5"/>
+        <v>1.125</v>
+      </c>
+      <c r="H17">
+        <v>13</v>
+      </c>
+      <c r="I17">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="B18">
         <v>0.82</v>
       </c>
       <c r="D18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E18">
         <v>1.27</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>10.8</v>
+      </c>
+      <c r="I18">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <f t="shared" si="5"/>
+        <v>0.875</v>
+      </c>
+      <c r="H19">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I19">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <f t="shared" si="5"/>
+        <v>0.75</v>
+      </c>
+      <c r="H20">
+        <v>9.17</v>
+      </c>
+      <c r="I20">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <f>G20-1/8</f>
+        <v>0.625</v>
+      </c>
+      <c r="H21">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I21">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="H22">
+        <v>7.9</v>
+      </c>
+      <c r="I22">
+        <v>2.2799999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <f>G22-1/8</f>
+        <v>0.375</v>
+      </c>
+      <c r="H23">
+        <v>7.2</v>
+      </c>
+      <c r="I23">
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="H24">
+        <v>7.05</v>
+      </c>
+      <c r="I24">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="H25">
+        <v>6.9</v>
+      </c>
+      <c r="I25">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>6.7</v>
+      </c>
+      <c r="I26">
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>
